--- a/jobs/uconn-walkways/out/fee_workbook.xlsx
+++ b/jobs/uconn-walkways/out/fee_workbook.xlsx
@@ -456,7 +456,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Term: 1 months | Escalation: 5%/yr | Lock: a9a64e82bcc4</t>
+          <t>Term: 1 months | Escalation: 5%/yr | Lock: 77b64f13667b</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Kickoff; review 6-sheet CD Review set and photographs; clarification/RFI list to architect</t>
+          <t>Kickoff; review 6-sheet CD Review set; clarification/RFI list to architect</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Kickoff; review 6-sheet CD Review set and photographs; clarification/RFI list to architect</t>
+          <t>Kickoff; review 6-sheet CD Review set; clarification/RFI list to architect</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>The estimate is based on the six-sheet CD Review set dated 09/21/26 (CS101, A101, A102, A201, A202, A203) and photographs to be provided by the architect; repair methods and materials are priced per the keynotes and industry-standard practice for matching existing construction.</t>
+          <t>The estimate is based solely on the six-sheet CD Review set dated 09/21/26 (CS101, A101, A102, A201, A202, A203); no specifications or photographs have been provided. Repair methods and materials are priced per the keynotes and industry-standard practice for matching existing construction.</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>6-sheet CD Review set plus architect-provided photographs; no specifications</t>
+          <t>6-sheet CD Review set only; no specifications or photographs</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Quantities are measured from the 1/4-inch plans and elevations where dimensioned and otherwise quantified from the keynote extents and photographs; unit rates (per SF of repointing, per brick, per LF of cap) are shown so the Owner can adjust quantities if field conditions differ.</t>
+          <t>Quantities are measured from the 1/4-inch plans and elevations where dimensioned and otherwise quantified from the keynoted locations and extents on the drawings; unit rates (per SF of repointing, per brick, per LF of cap) are shown so the Owner can adjust quantities if field conditions differ.</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>The base fee is prepared from the drawings and photographs; one site visit to Storrs is offered as an optional add-alternate, priced separately, with mileage billed at cost.</t>
+          <t>The base fee is prepared from the drawings only; one site visit to Storrs to field-verify repair extents is offered as an optional add-alternate, priced separately, with mileage billed at cost.</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Base from drawings and photos; site visit optional</t>
+          <t>Base from drawings only; site visit optional</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
